--- a/docs/oc-mensuales/suministro-de-combustibles/sep-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/sep-2026.xlsx
@@ -562,7 +562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18073,7 +19217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18134,7 +19282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18195,7 +19347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +19412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +19477,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18378,7 +19542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18439,7 +19607,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +19672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18561,7 +19737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19802,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18744,7 +19932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18805,7 +19997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +20062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18927,7 +20127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18988,7 +20192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19049,7 +20257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19110,7 +20322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +20387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +20452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +20517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +20582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +20647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +20712,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +20842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19659,7 +20907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +21037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19842,7 +21102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +21167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +21232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20025,7 +21297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20086,7 +21362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20147,7 +21427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20208,7 +21492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20269,7 +21557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20330,7 +21622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +21687,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20452,7 +21752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +22012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +22077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +22142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +22207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +22272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21001,7 +22337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21062,7 +22402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +22467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21184,7 +22532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21245,7 +22597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +22662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21489,7 +22857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21550,7 +22922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21611,7 +22987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21672,7 +23052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21733,7 +23117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +23182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21855,7 +23247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21916,7 +23312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +23377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +23442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22099,7 +23507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22160,7 +23572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22221,7 +23637,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22282,7 +23702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22343,7 +23767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22404,7 +23832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +24027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22648,7 +24092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +24157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22770,7 +24222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22831,7 +24287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22892,7 +24352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22953,7 +24417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23014,7 +24482,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23075,7 +24547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23136,7 +24612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23197,7 +24677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23258,7 +24742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23319,7 +24807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23380,7 +24872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23441,7 +24937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23502,7 +25002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23563,7 +25067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23624,7 +25132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23685,7 +25197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23746,7 +25262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23807,7 +25327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23868,7 +25392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23929,7 +25457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23990,7 +25522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24051,7 +25587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24112,7 +25652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24173,7 +25717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24234,7 +25782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24295,7 +25847,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24356,7 +25912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24417,7 +25977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24478,7 +26042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24539,7 +26107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24600,7 +26172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24661,7 +26237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24722,7 +26302,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24783,7 +26367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24844,7 +26432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24905,7 +26497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24966,7 +26562,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25027,7 +26627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25088,7 +26692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25149,7 +26757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25210,7 +26822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25271,7 +26887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25332,7 +26952,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25393,7 +27017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25454,7 +27082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25515,7 +27147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25576,7 +27212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +27277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25698,7 +27342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25759,7 +27407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25820,7 +27472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25881,7 +27537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25942,7 +27602,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +27667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26064,7 +27732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26125,7 +27797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26186,7 +27862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26247,7 +27927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26308,7 +27992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26369,7 +28057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26430,7 +28122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26491,7 +28187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26552,7 +28252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26613,7 +28317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26674,7 +28382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +28447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26796,7 +28512,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26857,7 +28577,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26918,7 +28642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26979,7 +28707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27040,7 +28772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +28837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27162,7 +28902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27223,7 +28967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +29032,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27345,7 +29097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27406,7 +29162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27467,7 +29227,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +29292,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27589,7 +29357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27650,7 +29422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27711,7 +29487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27772,7 +29552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27833,7 +29617,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27894,7 +29682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +29812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28077,7 +29877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28138,7 +29942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28199,7 +30007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28260,7 +30072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28321,7 +30137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28382,7 +30202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +30267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28504,7 +30332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +30397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28626,7 +30462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28687,7 +30527,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28748,7 +30592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +30657,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28870,7 +30722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28992,7 +30852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +30917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29114,7 +30982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +31047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +31112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29297,7 +31177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +31242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29419,7 +31307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29480,7 +31372,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +31437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +31502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +31567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29724,7 +31632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29785,7 +31697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +31762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +31827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30090,7 +32022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +32087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +32152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +32217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +32282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +32347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +32412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30517,7 +32477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +32542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +32607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +32672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +32737,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30883,7 +32867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30944,7 +32932,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31005,7 +32997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +33062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +33127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +33192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31249,7 +33257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31310,7 +33322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +33387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +33452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31493,7 +33517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +33582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +33647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31676,7 +33712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31798,7 +33842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31859,7 +33907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31920,7 +33972,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +34037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +34102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +34167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32164,7 +34232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32225,7 +34297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32286,7 +34362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32347,7 +34427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32408,7 +34492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +34557,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32530,7 +34622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32591,7 +34687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32652,7 +34752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32713,7 +34817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32774,7 +34882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32835,7 +34947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32896,7 +35012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32957,7 +35077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33018,7 +35142,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33079,7 +35207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33140,7 +35272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33201,7 +35337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +35402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33323,7 +35467,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33384,7 +35532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +35597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33506,7 +35662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33567,7 +35727,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33628,7 +35792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33689,7 +35857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33811,7 +35987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33872,7 +36052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33933,7 +36117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33994,7 +36182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34055,7 +36247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34116,7 +36312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34177,7 +36377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34238,7 +36442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34299,7 +36507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34360,7 +36572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34421,7 +36637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34482,7 +36702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34543,7 +36767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36897,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34726,7 +36962,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +37027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34848,7 +37092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34909,7 +37157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34970,7 +37222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35031,7 +37287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35092,7 +37352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35153,7 +37417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35214,7 +37482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35275,7 +37547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35336,7 +37612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K572" t="inlineStr"/>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L572" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35397,7 +37677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35519,7 +37807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +37872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35641,7 +37937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35702,7 +38002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35763,7 +38067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35824,7 +38132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35885,7 +38197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35946,7 +38262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36007,7 +38327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36068,7 +38392,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +38457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36190,7 +38522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36251,7 +38587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +38652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +38717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +38782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36495,7 +38847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36556,7 +38912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36617,7 +38977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36678,7 +39042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36739,7 +39107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +39172,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +39237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36922,7 +39302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36983,7 +39367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37044,7 +39432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37105,7 +39497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37166,7 +39562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +39627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37288,7 +39692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37349,7 +39757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37410,7 +39822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37471,7 +39887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37532,7 +39952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37593,7 +40017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +40082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37715,7 +40147,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K611" t="inlineStr"/>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L611" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37776,7 +40212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K612" t="inlineStr"/>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L612" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37837,7 +40277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37898,7 +40342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +40407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38020,7 +40472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38081,7 +40537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38142,7 +40602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38203,7 +40667,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +40732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38325,7 +40797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +40862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38447,7 +40927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40992,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38569,7 +41057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38630,7 +41122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +41187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +41252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38813,7 +41317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38874,7 +41382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +41447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38996,7 +41512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39057,7 +41577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39118,7 +41642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39179,7 +41707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39240,7 +41772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39301,7 +41837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39362,7 +41902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39423,7 +41967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39484,7 +42032,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39545,7 +42097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39606,7 +42162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39667,7 +42227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39728,7 +42292,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39789,7 +42357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39850,7 +42422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39911,7 +42487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39972,7 +42552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40033,7 +42617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40094,7 +42682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40155,7 +42747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40216,7 +42812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40277,7 +42877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40338,7 +42942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40399,7 +43007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40460,7 +43072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40521,7 +43137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40582,7 +43202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40643,7 +43267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40704,7 +43332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40765,7 +43397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40826,7 +43462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40887,7 +43527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40948,7 +43592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41009,7 +43657,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41070,7 +43722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41131,7 +43787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41192,7 +43852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41253,7 +43917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41314,7 +43982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41375,7 +44047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41436,7 +44112,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41497,7 +44177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41558,7 +44242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41619,7 +44307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41680,7 +44372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41741,7 +44437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41802,7 +44502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41863,7 +44567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41924,7 +44632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41985,7 +44697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42046,7 +44762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42107,7 +44827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42168,7 +44892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42229,7 +44957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42290,7 +45022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42351,7 +45087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42412,7 +45152,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42473,7 +45217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42534,7 +45282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42595,7 +45347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42656,7 +45412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42717,7 +45477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42778,7 +45542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42839,7 +45607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42900,7 +45672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42961,7 +45737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43022,7 +45802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43083,7 +45867,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43144,7 +45932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43205,7 +45997,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43266,7 +46062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43327,7 +46127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43388,7 +46192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43449,7 +46257,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43510,7 +46322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43571,7 +46387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43632,7 +46452,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43693,7 +46517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43754,7 +46582,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43815,7 +46647,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43876,7 +46712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43937,7 +46777,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43998,7 +46842,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44059,7 +46907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44120,7 +46972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44181,7 +47037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44242,7 +47102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44303,7 +47167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44364,7 +47232,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44425,7 +47297,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44486,7 +47362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44547,7 +47427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44608,7 +47492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K724" t="inlineStr"/>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L724" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44669,7 +47557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44730,7 +47622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44791,7 +47687,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44852,7 +47752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44913,7 +47817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44974,7 +47882,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45035,7 +47947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45096,7 +48012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45157,7 +48077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45218,7 +48142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45279,7 +48207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45340,7 +48272,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45401,7 +48337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45462,7 +48402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45523,7 +48467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45584,7 +48532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45645,7 +48597,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45706,7 +48662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45767,7 +48727,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45828,7 +48792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45889,7 +48857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45950,7 +48922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46011,7 +48987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/suministro-de-combustibles/sep-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/sep-2026.xlsx
@@ -6839,7 +6839,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -22699,7 +22699,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -48569,7 +48569,7 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
